--- a/sample_data/demo_ovs_sap.xlsx
+++ b/sample_data/demo_ovs_sap.xlsx
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
